--- a/resources/templates/standard/M1200-04.xlsx
+++ b/resources/templates/standard/M1200-04.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>공정 및 납입용기 관리 기준</t>
   </si>
@@ -682,11 +685,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -820,17 +825,17 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -839,12 +844,12 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
@@ -852,7 +857,7 @@
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4" s="5"/>
       <c r="Y4" s="5"/>
@@ -864,7 +869,7 @@
       <c r="AE4" s="5"/>
       <c r="AF4" s="5"/>
       <c r="AG4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
@@ -873,7 +878,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
       <c r="AN4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO4" s="5"/>
       <c r="AP4" s="5"/>
@@ -1601,7 +1606,7 @@
     </row>
     <row r="21" ht="21.95" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -1696,7 +1701,7 @@
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -1830,17 +1835,17 @@
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
       <c r="G26" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
@@ -1848,7 +1853,7 @@
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
       <c r="M26" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N26" s="19"/>
       <c r="O26" s="19"/>
@@ -1856,7 +1861,7 @@
       <c r="Q26" s="19"/>
       <c r="R26" s="19"/>
       <c r="S26" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T26" s="19"/>
       <c r="U26" s="19"/>
@@ -1872,19 +1877,19 @@
       <c r="AE26" s="19"/>
       <c r="AF26" s="19"/>
       <c r="AG26" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH26" s="19"/>
       <c r="AI26" s="19"/>
       <c r="AJ26" s="19"/>
       <c r="AK26" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL26" s="19"/>
       <c r="AM26" s="19"/>
       <c r="AN26" s="19"/>
       <c r="AO26" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP26" s="19"/>
       <c r="AQ26" s="19"/>
@@ -1905,7 +1910,7 @@
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
       <c r="M27" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N27" s="21"/>
       <c r="O27" s="21"/>
@@ -1952,7 +1957,7 @@
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
       <c r="M28" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N28" s="21"/>
       <c r="O28" s="21"/>
@@ -1999,7 +2004,7 @@
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="M29" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N29" s="21"/>
       <c r="O29" s="21"/>
@@ -2046,7 +2051,7 @@
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
       <c r="M30" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N30" s="21"/>
       <c r="O30" s="21"/>
@@ -2095,7 +2100,7 @@
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
       <c r="M31" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N31" s="21"/>
       <c r="O31" s="21"/>
@@ -2142,7 +2147,7 @@
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
       <c r="M32" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N32" s="21"/>
       <c r="O32" s="21"/>
@@ -2189,7 +2194,7 @@
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
       <c r="M33" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="21"/>
       <c r="O33" s="21"/>
@@ -2236,7 +2241,7 @@
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
       <c r="M34" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N34" s="21"/>
       <c r="O34" s="21"/>
@@ -2285,7 +2290,7 @@
       <c r="K35" s="21"/>
       <c r="L35" s="21"/>
       <c r="M35" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N35" s="21"/>
       <c r="O35" s="21"/>
@@ -2332,7 +2337,7 @@
       <c r="K36" s="21"/>
       <c r="L36" s="21"/>
       <c r="M36" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N36" s="21"/>
       <c r="O36" s="21"/>
@@ -2379,7 +2384,7 @@
       <c r="K37" s="21"/>
       <c r="L37" s="21"/>
       <c r="M37" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N37" s="21"/>
       <c r="O37" s="21"/>
@@ -2426,7 +2431,7 @@
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
       <c r="M38" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N38" s="21"/>
       <c r="O38" s="21"/>
@@ -2475,7 +2480,7 @@
       <c r="K39" s="21"/>
       <c r="L39" s="21"/>
       <c r="M39" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N39" s="21"/>
       <c r="O39" s="21"/>
@@ -2522,7 +2527,7 @@
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
       <c r="M40" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N40" s="21"/>
       <c r="O40" s="21"/>
@@ -2569,7 +2574,7 @@
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
       <c r="M41" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N41" s="21"/>
       <c r="O41" s="21"/>
@@ -2616,7 +2621,7 @@
       <c r="K42" s="21"/>
       <c r="L42" s="21"/>
       <c r="M42" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N42" s="21"/>
       <c r="O42" s="21"/>
@@ -2665,7 +2670,7 @@
       <c r="K43" s="21"/>
       <c r="L43" s="21"/>
       <c r="M43" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N43" s="21"/>
       <c r="O43" s="21"/>
@@ -2712,7 +2717,7 @@
       <c r="K44" s="21"/>
       <c r="L44" s="21"/>
       <c r="M44" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N44" s="21"/>
       <c r="O44" s="21"/>
@@ -2759,7 +2764,7 @@
       <c r="K45" s="21"/>
       <c r="L45" s="21"/>
       <c r="M45" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N45" s="21"/>
       <c r="O45" s="21"/>
@@ -2806,7 +2811,7 @@
       <c r="K46" s="21"/>
       <c r="L46" s="21"/>
       <c r="M46" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N46" s="21"/>
       <c r="O46" s="21"/>
@@ -2855,7 +2860,7 @@
       <c r="K47" s="21"/>
       <c r="L47" s="21"/>
       <c r="M47" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N47" s="21"/>
       <c r="O47" s="21"/>
@@ -2902,7 +2907,7 @@
       <c r="K48" s="21"/>
       <c r="L48" s="21"/>
       <c r="M48" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N48" s="21"/>
       <c r="O48" s="21"/>
@@ -2949,7 +2954,7 @@
       <c r="K49" s="21"/>
       <c r="L49" s="21"/>
       <c r="M49" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N49" s="21"/>
       <c r="O49" s="21"/>
@@ -2996,7 +3001,7 @@
       <c r="K50" s="21"/>
       <c r="L50" s="21"/>
       <c r="M50" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N50" s="23"/>
       <c r="O50" s="23"/>
